--- a/data/tuning COM translasi pitch 1 kaki.xlsx
+++ b/data/tuning COM translasi pitch 1 kaki.xlsx
@@ -470,25 +470,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.118</v>
+        <v>0.123</v>
       </c>
       <c r="C2" t="n">
-        <v>-9.593</v>
+        <v>0.661</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>198.868</v>
+        <v>197.587</v>
       </c>
       <c r="F2" t="n">
         <v>12.945</v>
       </c>
       <c r="G2" t="n">
-        <v>6.346</v>
+        <v>15.197</v>
       </c>
       <c r="H2" t="n">
-        <v>200.73</v>
+        <v>200.166</v>
       </c>
     </row>
     <row r="3">
@@ -496,25 +496,25 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>108.418</v>
+        <v>110.492</v>
       </c>
       <c r="C3" t="n">
-        <v>-9.593</v>
+        <v>0.661</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>198.868</v>
+        <v>197.587</v>
       </c>
       <c r="F3" t="n">
         <v>12.945</v>
       </c>
       <c r="G3" t="n">
-        <v>6.346</v>
+        <v>15.197</v>
       </c>
       <c r="H3" t="n">
-        <v>200.73</v>
+        <v>200.166</v>
       </c>
     </row>
     <row r="4">
@@ -522,25 +522,25 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>219.209</v>
+        <v>220.042</v>
       </c>
       <c r="C4" t="n">
-        <v>-9.593</v>
+        <v>0.661</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>198.868</v>
+        <v>197.587</v>
       </c>
       <c r="F4" t="n">
         <v>10.373</v>
       </c>
       <c r="G4" t="n">
-        <v>6.094</v>
+        <v>14.899</v>
       </c>
       <c r="H4" t="n">
-        <v>199.852</v>
+        <v>199.302</v>
       </c>
     </row>
     <row r="5">
@@ -548,25 +548,25 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>331.247</v>
+        <v>331.914</v>
       </c>
       <c r="C5" t="n">
-        <v>-9.593</v>
+        <v>0.661</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>198.868</v>
+        <v>197.587</v>
       </c>
       <c r="F5" t="n">
-        <v>9.113</v>
+        <v>8.49</v>
       </c>
       <c r="G5" t="n">
-        <v>5.95</v>
+        <v>14.638</v>
       </c>
       <c r="H5" t="n">
-        <v>199.348</v>
+        <v>198.544</v>
       </c>
     </row>
     <row r="6">
@@ -574,25 +574,25 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>443.331</v>
+        <v>444.419</v>
       </c>
       <c r="C6" t="n">
-        <v>-9.593</v>
+        <v>0.661</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>198.868</v>
+        <v>197.587</v>
       </c>
       <c r="F6" t="n">
-        <v>9.113</v>
+        <v>8.49</v>
       </c>
       <c r="G6" t="n">
-        <v>5.95</v>
+        <v>14.638</v>
       </c>
       <c r="H6" t="n">
-        <v>199.348</v>
+        <v>198.544</v>
       </c>
     </row>
     <row r="7">
@@ -600,25 +600,25 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>555.439</v>
+        <v>555.83</v>
       </c>
       <c r="C7" t="n">
-        <v>-9.593</v>
+        <v>0.661</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>198.868</v>
+        <v>197.587</v>
       </c>
       <c r="F7" t="n">
-        <v>9.741</v>
+        <v>9.113</v>
       </c>
       <c r="G7" t="n">
-        <v>6.024</v>
+        <v>14.729</v>
       </c>
       <c r="H7" t="n">
-        <v>199.605</v>
+        <v>198.807</v>
       </c>
     </row>
     <row r="8">
@@ -626,25 +626,25 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>667.268</v>
+        <v>668.207</v>
       </c>
       <c r="C8" t="n">
-        <v>-9.593</v>
+        <v>0.661</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>198.868</v>
+        <v>197.587</v>
       </c>
       <c r="F8" t="n">
-        <v>6.906</v>
+        <v>6.283</v>
       </c>
       <c r="G8" t="n">
-        <v>6.07</v>
+        <v>14.78</v>
       </c>
       <c r="H8" t="n">
-        <v>199.768</v>
+        <v>198.956</v>
       </c>
     </row>
     <row r="9">
@@ -652,25 +652,25 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>779.992</v>
+        <v>780.511</v>
       </c>
       <c r="C9" t="n">
-        <v>-9.593</v>
+        <v>0.661</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>198.868</v>
+        <v>197.587</v>
       </c>
       <c r="F9" t="n">
-        <v>6.906</v>
+        <v>6.283</v>
       </c>
       <c r="G9" t="n">
-        <v>6.07</v>
+        <v>14.78</v>
       </c>
       <c r="H9" t="n">
-        <v>199.768</v>
+        <v>198.956</v>
       </c>
     </row>
     <row r="10">
@@ -678,25 +678,25 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>891.6130000000001</v>
+        <v>892.131</v>
       </c>
       <c r="C10" t="n">
-        <v>-9.593</v>
+        <v>0.661</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>198.868</v>
+        <v>197.587</v>
       </c>
       <c r="F10" t="n">
-        <v>5.321</v>
+        <v>6.283</v>
       </c>
       <c r="G10" t="n">
-        <v>6.253</v>
+        <v>14.78</v>
       </c>
       <c r="H10" t="n">
-        <v>200.407</v>
+        <v>198.956</v>
       </c>
     </row>
     <row r="11">
@@ -704,25 +704,25 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1003.67</v>
+        <v>1004.007</v>
       </c>
       <c r="C11" t="n">
-        <v>-9.593</v>
+        <v>0.661</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>198.868</v>
+        <v>197.587</v>
       </c>
       <c r="F11" t="n">
-        <v>3.1</v>
+        <v>6.283</v>
       </c>
       <c r="G11" t="n">
-        <v>6.352</v>
+        <v>14.78</v>
       </c>
       <c r="H11" t="n">
-        <v>200.751</v>
+        <v>198.956</v>
       </c>
     </row>
     <row r="12">
@@ -730,25 +730,25 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1115.419</v>
+        <v>1118.316</v>
       </c>
       <c r="C12" t="n">
-        <v>-9.593</v>
+        <v>0.661</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>198.868</v>
+        <v>197.587</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.608</v>
+        <v>6.283</v>
       </c>
       <c r="G12" t="n">
-        <v>6.368</v>
+        <v>14.78</v>
       </c>
       <c r="H12" t="n">
-        <v>200.805</v>
+        <v>198.956</v>
       </c>
     </row>
     <row r="13">
@@ -756,25 +756,25 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1227.517</v>
+        <v>1228.087</v>
       </c>
       <c r="C13" t="n">
-        <v>-9.593</v>
+        <v>0.661</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>198.868</v>
+        <v>197.587</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.462</v>
+        <v>6.906</v>
       </c>
       <c r="G13" t="n">
-        <v>6.355</v>
+        <v>14.871</v>
       </c>
       <c r="H13" t="n">
-        <v>200.76</v>
+        <v>199.219</v>
       </c>
     </row>
     <row r="14">
@@ -782,25 +782,25 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1339.221</v>
+        <v>1339.888</v>
       </c>
       <c r="C14" t="n">
-        <v>-9.593</v>
+        <v>0.661</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>198.868</v>
+        <v>197.587</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.412</v>
+        <v>6.906</v>
       </c>
       <c r="G14" t="n">
-        <v>6.322</v>
+        <v>14.871</v>
       </c>
       <c r="H14" t="n">
-        <v>200.646</v>
+        <v>199.219</v>
       </c>
     </row>
     <row r="15">
@@ -808,25 +808,25 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1451.437</v>
+        <v>1451.847</v>
       </c>
       <c r="C15" t="n">
-        <v>-9.593</v>
+        <v>0.661</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>198.868</v>
+        <v>197.587</v>
       </c>
       <c r="F15" t="n">
-        <v>-16.261</v>
+        <v>6.906</v>
       </c>
       <c r="G15" t="n">
-        <v>6.257</v>
+        <v>14.871</v>
       </c>
       <c r="H15" t="n">
-        <v>200.42</v>
+        <v>199.219</v>
       </c>
     </row>
     <row r="16">
@@ -834,25 +834,25 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1563.344</v>
+        <v>1564.007</v>
       </c>
       <c r="C16" t="n">
-        <v>-9.593</v>
+        <v>0.661</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>198.868</v>
+        <v>197.587</v>
       </c>
       <c r="F16" t="n">
-        <v>-21.356</v>
+        <v>6.906</v>
       </c>
       <c r="G16" t="n">
-        <v>6.181</v>
+        <v>14.871</v>
       </c>
       <c r="H16" t="n">
-        <v>200.153</v>
+        <v>199.219</v>
       </c>
     </row>
     <row r="17">
@@ -860,25 +860,25 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1675.351</v>
+        <v>1677.972</v>
       </c>
       <c r="C17" t="n">
-        <v>-9.593</v>
+        <v>0.661</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>198.868</v>
+        <v>197.587</v>
       </c>
       <c r="F17" t="n">
-        <v>-21.356</v>
+        <v>4.693</v>
       </c>
       <c r="G17" t="n">
-        <v>6.181</v>
+        <v>15</v>
       </c>
       <c r="H17" t="n">
-        <v>200.153</v>
+        <v>199.595</v>
       </c>
     </row>
     <row r="18">
@@ -886,25 +886,25 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1787.766</v>
+        <v>1787.881</v>
       </c>
       <c r="C18" t="n">
-        <v>-9.593</v>
+        <v>0.661</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>198.868</v>
+        <v>197.587</v>
       </c>
       <c r="F18" t="n">
-        <v>-24.195</v>
+        <v>4.693</v>
       </c>
       <c r="G18" t="n">
-        <v>9.015000000000001</v>
+        <v>15</v>
       </c>
       <c r="H18" t="n">
-        <v>199.662</v>
+        <v>199.595</v>
       </c>
     </row>
     <row r="19">
@@ -912,25 +912,25 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1899.246</v>
+        <v>1900.011</v>
       </c>
       <c r="C19" t="n">
-        <v>-9.593</v>
+        <v>0.661</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>198.868</v>
+        <v>197.587</v>
       </c>
       <c r="F19" t="n">
-        <v>-24.195</v>
+        <v>5.321</v>
       </c>
       <c r="G19" t="n">
-        <v>9.015000000000001</v>
+        <v>15.087</v>
       </c>
       <c r="H19" t="n">
-        <v>199.662</v>
+        <v>199.848</v>
       </c>
     </row>
     <row r="20">
@@ -938,25 +938,25 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2011.582</v>
+        <v>2012.17</v>
       </c>
       <c r="C20" t="n">
-        <v>-9.593</v>
+        <v>0.661</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>198.868</v>
+        <v>197.587</v>
       </c>
       <c r="F20" t="n">
-        <v>-24.195</v>
+        <v>2.472</v>
       </c>
       <c r="G20" t="n">
-        <v>9.015000000000001</v>
+        <v>15.117</v>
       </c>
       <c r="H20" t="n">
-        <v>199.662</v>
+        <v>199.934</v>
       </c>
     </row>
   </sheetData>
